--- a/samples/sample_team_entries.xlsx
+++ b/samples/sample_team_entries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew\Documents\Coding\Time-Keeper\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C7765B-BDEC-44A8-A4AD-0679537B13CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D48984E-A4D5-4C72-AB6F-C1596C3E751E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -34,6 +34,15 @@
   </si>
   <si>
     <t>time</t>
+  </si>
+  <si>
+    <t>MWT</t>
+  </si>
+  <si>
+    <t>ADL</t>
+  </si>
+  <si>
+    <t>XXL</t>
   </si>
 </sst>
 </file>
@@ -69,8 +78,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -351,8 +361,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -365,6 +378,94 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
